--- a/GameConfig/Datas/通用配置表/文本配置表.xlsx
+++ b/GameConfig/Datas/通用配置表/文本配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="通用文本" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -166,6 +166,15 @@
   </si>
   <si>
     <t>{0}小时前</t>
+  </si>
+  <si>
+    <t>{0}千</t>
+  </si>
+  <si>
+    <t>{0}万</t>
+  </si>
+  <si>
+    <t>{0}亿</t>
   </si>
   <si>
     <t>开始游戏</t>
@@ -994,7 +1003,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1054,9 +1063,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1400,13 +1406,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="24.5833333333333" style="3" customWidth="1"/>
     <col min="3" max="3" width="11" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.5833333333333" style="22" customWidth="1"/>
+    <col min="4" max="4" width="32.5833333333333" style="21" customWidth="1"/>
     <col min="5" max="5" width="34.0833333333333" style="3" customWidth="1"/>
     <col min="6" max="11" width="35.25" style="3" customWidth="1"/>
     <col min="12" max="12" width="17.75" style="3" customWidth="1"/>
@@ -1430,7 +1436,7 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -1483,7 +1489,7 @@
       <c r="C2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="24"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="14" t="s">
         <v>7</v>
       </c>
@@ -1530,7 +1536,7 @@
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="25"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
@@ -1579,7 +1585,7 @@
       <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="22" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -1628,7 +1634,7 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -2088,27 +2094,19 @@
       <c r="B29" s="3">
         <v>10000024</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="21"/>
+      <c r="E29" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F29" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>51</v>
-      </c>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
       <c r="P29" s="19"/>
       <c r="S29" s="19"/>
     </row>
@@ -2116,39 +2114,30 @@
       <c r="B30" s="3">
         <v>10000025</v>
       </c>
-      <c r="E30" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K30" s="19" t="s">
-        <v>58</v>
-      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
       <c r="P30" s="19"/>
       <c r="S30" s="19"/>
     </row>
-    <row r="31" s="3" customFormat="1" spans="2:19">
+    <row r="31" spans="2:19">
       <c r="B31" s="3">
-        <v>10100001</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>60</v>
+        <v>10000026</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
@@ -2161,70 +2150,87 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="3">
-        <v>10100002</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
+        <v>10000027</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>54</v>
+      </c>
       <c r="P32" s="19"/>
       <c r="S32" s="19"/>
     </row>
-    <row r="33" spans="2:19">
+    <row r="33" spans="1:19">
       <c r="B33" s="3">
-        <v>10100003</v>
-      </c>
-      <c r="D33" s="27" t="s">
+        <v>10000028</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>62</v>
+      <c r="J33" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="P33" s="19"/>
       <c r="S33" s="19"/>
     </row>
-    <row r="34" spans="2:19">
-      <c r="B34" s="3">
-        <v>10100004</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>63</v>
-      </c>
+    <row r="34" customFormat="1" spans="1:19">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="21"/>
+      <c r="E34" s="25"/>
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="P34" s="28"/>
+      <c r="P34" s="19"/>
       <c r="S34" s="19"/>
     </row>
-    <row r="35" spans="2:19">
+    <row r="35" s="3" customFormat="1" spans="1:19">
       <c r="B35" s="3">
-        <v>10100005</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>64</v>
+        <v>10100001</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>63</v>
       </c>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
@@ -2232,21 +2238,19 @@
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="P35" s="28"/>
+      <c r="P35" s="19"/>
       <c r="S35" s="19"/>
     </row>
-    <row r="36" spans="2:19">
+    <row r="36" spans="1:19">
       <c r="B36" s="3">
-        <v>10100006</v>
+        <v>10100002</v>
       </c>
       <c r="C36" s="19"/>
-      <c r="D36" s="27" t="s">
-        <v>59</v>
+      <c r="D36" s="26" t="s">
+        <v>62</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
@@ -2255,127 +2259,226 @@
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
       <c r="P36" s="19"/>
       <c r="S36" s="19"/>
     </row>
-    <row r="37" s="3" customFormat="1" spans="2:19">
+    <row r="37" spans="1:19">
       <c r="B37" s="3">
-        <v>11000001</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="27" t="s">
-        <v>66</v>
+        <v>10100003</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>62</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
+        <v>65</v>
+      </c>
       <c r="P37" s="19"/>
       <c r="S37" s="19"/>
     </row>
-    <row r="38" customFormat="1" spans="2:19">
+    <row r="38" spans="1:19">
       <c r="B38" s="3">
+        <v>10100004</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="P38" s="27"/>
+      <c r="S38" s="19"/>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="B39" s="3">
+        <v>10100005</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="P39" s="27"/>
+      <c r="S39" s="19"/>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="B40" s="3">
+        <v>10100006</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="S40" s="19"/>
+    </row>
+    <row r="41" customFormat="1" spans="1:19">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="S41" s="19"/>
+    </row>
+    <row r="42" s="3" customFormat="1" spans="1:19">
+      <c r="B42" s="3">
+        <v>11000001</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="S42" s="19"/>
+    </row>
+    <row r="43" customFormat="1" spans="1:19">
+      <c r="B43" s="3">
         <v>11000002</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19">
-      <c r="B39"/>
-      <c r="C39"/>
-      <c r="D39" s="29"/>
-      <c r="E39"/>
-    </row>
-    <row r="40" spans="2:19">
-      <c r="B40"/>
-      <c r="C40"/>
-      <c r="D40" s="29"/>
-      <c r="E40"/>
-    </row>
-    <row r="41" spans="2:19">
-      <c r="B41"/>
-      <c r="C41"/>
-      <c r="D41" s="29"/>
-      <c r="E41"/>
-    </row>
-    <row r="42" spans="2:19">
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42" s="29"/>
-      <c r="E42"/>
-    </row>
-    <row r="43" spans="2:19">
-      <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43" s="29"/>
-      <c r="E43"/>
-    </row>
-    <row r="44" spans="2:19">
+      <c r="C43" s="3"/>
+      <c r="D43" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
       <c r="B44"/>
       <c r="C44"/>
-      <c r="D44" s="29"/>
+      <c r="D44" s="28"/>
       <c r="E44"/>
     </row>
-    <row r="45" spans="2:19">
+    <row r="45" spans="1:19">
       <c r="B45"/>
       <c r="C45"/>
-      <c r="D45" s="29"/>
+      <c r="D45" s="28"/>
       <c r="E45"/>
     </row>
-    <row r="46" spans="2:19">
+    <row r="46" spans="1:19">
       <c r="B46"/>
       <c r="C46"/>
-      <c r="D46" s="29"/>
+      <c r="D46" s="28"/>
       <c r="E46"/>
     </row>
-    <row r="47" spans="2:19">
+    <row r="47" spans="1:19">
       <c r="B47"/>
       <c r="C47"/>
-      <c r="D47" s="29"/>
+      <c r="D47" s="28"/>
       <c r="E47"/>
     </row>
-    <row r="48" spans="2:19">
+    <row r="48" spans="1:19">
       <c r="B48"/>
       <c r="C48"/>
-      <c r="D48" s="29"/>
+      <c r="D48" s="28"/>
       <c r="E48"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49"/>
       <c r="C49"/>
-      <c r="D49" s="29"/>
+      <c r="D49" s="28"/>
       <c r="E49"/>
     </row>
     <row r="50" spans="2:5">
       <c r="B50"/>
       <c r="C50"/>
-      <c r="D50" s="29"/>
+      <c r="D50" s="28"/>
       <c r="E50"/>
     </row>
     <row r="51" spans="2:5">
       <c r="B51"/>
       <c r="C51"/>
-      <c r="D51" s="29"/>
+      <c r="D51" s="28"/>
       <c r="E51"/>
     </row>
     <row r="52" spans="2:5">
       <c r="B52"/>
       <c r="C52"/>
-      <c r="D52" s="29"/>
+      <c r="D52" s="28"/>
       <c r="E52"/>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53" s="28"/>
+      <c r="E53"/>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54" s="28"/>
+      <c r="E54"/>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55" s="28"/>
+      <c r="E55"/>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56" s="28"/>
+      <c r="E56"/>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57" s="28"/>
+      <c r="E57"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2609,7 +2712,7 @@
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>15</v>
@@ -2669,10 +2772,10 @@
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -2681,10 +2784,10 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -2693,10 +2796,10 @@
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -2705,10 +2808,10 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -2717,10 +2820,10 @@
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -2729,10 +2832,10 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:41">
@@ -2741,10 +2844,10 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:41">
@@ -2753,10 +2856,10 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -2765,10 +2868,10 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:41">
@@ -2777,10 +2880,10 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:41">
@@ -2789,10 +2892,10 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2801,10 +2904,10 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2813,10 +2916,10 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2825,32 +2928,31 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" s="21" customFormat="1" spans="1:5">
-      <c r="A20" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="20"/>
-      <c r="E20" s="3"/>
     </row>
     <row r="21" customFormat="1" spans="1:5">
       <c r="B21" s="3">
         <v>41000001</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2858,10 +2960,10 @@
         <v>41000002</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2869,10 +2971,10 @@
         <v>41000003</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2880,10 +2982,10 @@
         <v>41000004</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3099,7 +3201,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>13</v>
@@ -3148,7 +3250,7 @@
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>15</v>
@@ -3434,7 +3536,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>13</v>
@@ -3483,7 +3585,7 @@
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>15</v>
@@ -3772,7 +3874,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>13</v>
@@ -3821,7 +3923,7 @@
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>15</v>
@@ -3880,7 +3982,7 @@
         <v>1001</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -3888,7 +3990,7 @@
         <v>1002</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -3896,7 +3998,7 @@
         <v>1003</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -3904,7 +4006,7 @@
         <v>1004</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="4:4">

--- a/GameConfig/Datas/通用配置表/文本配置表.xlsx
+++ b/GameConfig/Datas/通用配置表/文本配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="通用文本" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,9 @@
     <sheet name="自动生成组件文本" sheetId="4" r:id="rId4"/>
     <sheet name="登录错误_服务器" sheetId="2" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,8 +33,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
   <si>
     <t>##var</t>
   </si>
@@ -63,6 +88,9 @@
     <t>##</t>
   </si>
   <si>
+    <t>内容是 string 数组类型，数组索引对应 LocalizationType 枚举</t>
+  </si>
+  <si>
     <t>文本ID</t>
   </si>
   <si>
@@ -72,31 +100,7 @@
     <t>备注:文本ID的第2和3位区分系统</t>
   </si>
   <si>
-    <t>内容是 string 数组类型，数组索引对应 LocalizationType 枚举</t>
-  </si>
-  <si>
     <t>自定义的文本ID是1开头</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>GAT</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>JP</t>
-  </si>
-  <si>
-    <t>VN</t>
-  </si>
-  <si>
-    <t>INDO</t>
   </si>
   <si>
     <t>{0}天{1}时{2}分</t>
@@ -1148,6 +1152,114 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="通用"/>
+      <sheetName val="货币枚举"/>
+      <sheetName val="音效枚举"/>
+      <sheetName val="特效枚举"/>
+      <sheetName val="语言地区"/>
+      <sheetName val="活动开启类型"/>
+      <sheetName val="活动类型枚举"/>
+      <sheetName val="系统开放类型"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="2">
+          <cell r="J2" t="str">
+            <v>value</v>
+          </cell>
+          <cell r="K2" t="str">
+            <v>comment</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="J3" t="str">
+            <v>值</v>
+          </cell>
+          <cell r="K3" t="str">
+            <v>注释</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>0</v>
+          </cell>
+          <cell r="K4" t="str">
+            <v>中国</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1</v>
+          </cell>
+          <cell r="K5" t="str">
+            <v>欧美</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2</v>
+          </cell>
+          <cell r="K6" t="str">
+            <v>港澳台</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>3</v>
+          </cell>
+          <cell r="K7" t="str">
+            <v>韩国</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="J8">
+            <v>4</v>
+          </cell>
+          <cell r="K8" t="str">
+            <v>日本</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="J9">
+            <v>5</v>
+          </cell>
+          <cell r="K9" t="str">
+            <v>越南</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="J10">
+            <v>6</v>
+          </cell>
+          <cell r="K10" t="str">
+            <v>印尼</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="J11">
+            <v>7</v>
+          </cell>
+          <cell r="K11" t="str">
+            <v>占位符（新增+1）</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1406,7 +1518,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AO58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -1579,17 +1691,11 @@
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -1632,31 +1738,35 @@
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="D5" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8">
+        <v>3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="8">
+        <v>5</v>
+      </c>
+      <c r="K5" s="8">
+        <v>6</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
@@ -1689,34 +1799,83 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" spans="1:41">
-      <c r="B6" s="3">
-        <v>10000001</v>
-      </c>
-      <c r="C6" s="3">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="S6" s="19"/>
+    <row r="6" s="1" customFormat="1" spans="1:41">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="str" cm="1">
+        <f t="array" ref="E6">INDEX([1]语言地区!$K:$K,MATCH(E5,[1]语言地区!$J:$J,0))</f>
+        <v>中国</v>
+      </c>
+      <c r="F6" s="8" t="str" cm="1">
+        <f t="array" ref="F6">INDEX([1]语言地区!$K:$K,MATCH(F5,[1]语言地区!$J:$J,0))</f>
+        <v>欧美</v>
+      </c>
+      <c r="G6" s="8" t="str" cm="1">
+        <f t="array" ref="G6">INDEX([1]语言地区!$K:$K,MATCH(G5,[1]语言地区!$J:$J,0))</f>
+        <v>港澳台</v>
+      </c>
+      <c r="H6" s="8" t="str" cm="1">
+        <f t="array" ref="H6">INDEX([1]语言地区!$K:$K,MATCH(H5,[1]语言地区!$J:$J,0))</f>
+        <v>韩国</v>
+      </c>
+      <c r="I6" s="8" t="str" cm="1">
+        <f t="array" ref="I6">INDEX([1]语言地区!$K:$K,MATCH(I5,[1]语言地区!$J:$J,0))</f>
+        <v>日本</v>
+      </c>
+      <c r="J6" s="8" t="str" cm="1">
+        <f t="array" ref="J6">INDEX([1]语言地区!$K:$K,MATCH(J5,[1]语言地区!$J:$J,0))</f>
+        <v>越南</v>
+      </c>
+      <c r="K6" s="8" t="str" cm="1">
+        <f t="array" ref="K6">INDEX([1]语言地区!$K:$K,MATCH(K5,[1]语言地区!$J:$J,0))</f>
+        <v>印尼</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
     </row>
     <row r="7" spans="1:41">
       <c r="B7" s="3">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="C7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
@@ -1729,13 +1888,13 @@
     </row>
     <row r="8" spans="1:41">
       <c r="B8" s="3">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="C8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
@@ -1748,13 +1907,13 @@
     </row>
     <row r="9" spans="1:41">
       <c r="B9" s="3">
-        <v>10000004</v>
+        <v>10000003</v>
       </c>
       <c r="C9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F9" s="19"/>
       <c r="G9" s="19"/>
@@ -1767,13 +1926,13 @@
     </row>
     <row r="10" spans="1:41">
       <c r="B10" s="3">
-        <v>10000005</v>
+        <v>10000004</v>
       </c>
       <c r="C10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
@@ -1786,13 +1945,13 @@
     </row>
     <row r="11" spans="1:41">
       <c r="B11" s="3">
-        <v>10000006</v>
+        <v>10000005</v>
       </c>
       <c r="C11" s="3">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
@@ -1805,13 +1964,13 @@
     </row>
     <row r="12" spans="1:41">
       <c r="B12" s="3">
-        <v>10000007</v>
+        <v>10000006</v>
       </c>
       <c r="C12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
@@ -1824,10 +1983,13 @@
     </row>
     <row r="13" spans="1:41">
       <c r="B13" s="3">
-        <v>10000008</v>
+        <v>10000007</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
@@ -1840,10 +2002,10 @@
     </row>
     <row r="14" spans="1:41">
       <c r="B14" s="3">
-        <v>10000009</v>
+        <v>10000008</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
@@ -1856,10 +2018,10 @@
     </row>
     <row r="15" spans="1:41">
       <c r="B15" s="3">
-        <v>10000010</v>
+        <v>10000009</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
@@ -1872,10 +2034,10 @@
     </row>
     <row r="16" spans="1:41">
       <c r="B16" s="3">
-        <v>10000011</v>
+        <v>10000010</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
@@ -1888,10 +2050,10 @@
     </row>
     <row r="17" spans="2:19">
       <c r="B17" s="3">
-        <v>10000012</v>
+        <v>10000011</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -1904,10 +2066,10 @@
     </row>
     <row r="18" spans="2:19">
       <c r="B18" s="3">
-        <v>10000013</v>
+        <v>10000012</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F18" s="19"/>
       <c r="G18" s="19"/>
@@ -1920,10 +2082,10 @@
     </row>
     <row r="19" spans="2:19">
       <c r="B19" s="3">
-        <v>10000014</v>
+        <v>10000013</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
@@ -1936,10 +2098,10 @@
     </row>
     <row r="20" spans="2:19">
       <c r="B20" s="3">
-        <v>10000015</v>
+        <v>10000014</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
@@ -1952,10 +2114,10 @@
     </row>
     <row r="21" spans="2:19">
       <c r="B21" s="3">
-        <v>10000016</v>
+        <v>10000015</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
@@ -1968,10 +2130,10 @@
     </row>
     <row r="22" spans="2:19">
       <c r="B22" s="3">
-        <v>10000017</v>
+        <v>10000016</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F22" s="19"/>
       <c r="G22" s="19"/>
@@ -1984,10 +2146,10 @@
     </row>
     <row r="23" spans="2:19">
       <c r="B23" s="3">
-        <v>10000018</v>
+        <v>10000017</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
@@ -2000,10 +2162,10 @@
     </row>
     <row r="24" spans="2:19">
       <c r="B24" s="3">
-        <v>10000019</v>
+        <v>10000018</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
@@ -2016,13 +2178,10 @@
     </row>
     <row r="25" spans="2:19">
       <c r="B25" s="3">
-        <v>10000020</v>
-      </c>
-      <c r="C25" s="3">
-        <v>1</v>
+        <v>10000019</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
@@ -2035,13 +2194,13 @@
     </row>
     <row r="26" spans="2:19">
       <c r="B26" s="3">
-        <v>10000021</v>
+        <v>10000020</v>
       </c>
       <c r="C26" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
@@ -2054,13 +2213,13 @@
     </row>
     <row r="27" spans="2:19">
       <c r="B27" s="3">
-        <v>10000022</v>
+        <v>10000021</v>
       </c>
       <c r="C27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
@@ -2073,13 +2232,13 @@
     </row>
     <row r="28" spans="2:19">
       <c r="B28" s="3">
-        <v>10000023</v>
+        <v>10000022</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
@@ -2092,14 +2251,13 @@
     </row>
     <row r="29" spans="2:19">
       <c r="B29" s="3">
-        <v>10000024</v>
+        <v>10000023</v>
       </c>
       <c r="C29" s="3">
         <v>1</v>
       </c>
-      <c r="D29" s="21"/>
       <c r="E29" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
@@ -2112,13 +2270,13 @@
     </row>
     <row r="30" spans="2:19">
       <c r="B30" s="3">
-        <v>10000025</v>
+        <v>10000024</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
@@ -2131,13 +2289,13 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="3">
-        <v>10000026</v>
+        <v>10000025</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
@@ -2150,88 +2308,88 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="3">
-        <v>10000027</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="K32" s="19" t="s">
-        <v>54</v>
-      </c>
+        <v>10000026</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
       <c r="P32" s="19"/>
       <c r="S32" s="19"/>
     </row>
     <row r="33" spans="1:19">
       <c r="B33" s="3">
-        <v>10000028</v>
+        <v>10000027</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K33" s="19" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="P33" s="19"/>
       <c r="S33" s="19"/>
     </row>
-    <row r="34" customFormat="1" spans="1:19">
-      <c r="A34" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
+    <row r="34" spans="1:19">
+      <c r="B34" s="3">
+        <v>10000028</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>54</v>
+      </c>
       <c r="P34" s="19"/>
       <c r="S34" s="19"/>
     </row>
-    <row r="35" s="3" customFormat="1" spans="1:19">
-      <c r="B35" s="3">
-        <v>10100001</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>63</v>
-      </c>
+    <row r="35" customFormat="1" spans="1:19">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="21"/>
+      <c r="E35" s="25"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
@@ -2241,16 +2399,15 @@
       <c r="P35" s="19"/>
       <c r="S35" s="19"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" s="3" customFormat="1" spans="1:19">
       <c r="B36" s="3">
-        <v>10100002</v>
-      </c>
-      <c r="C36" s="19"/>
+        <v>10100001</v>
+      </c>
       <c r="D36" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>56</v>
       </c>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
@@ -2258,55 +2415,53 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
       <c r="P36" s="19"/>
       <c r="S36" s="19"/>
     </row>
     <row r="37" spans="1:19">
       <c r="B37" s="3">
-        <v>10100003</v>
-      </c>
+        <v>10100002</v>
+      </c>
+      <c r="C37" s="19"/>
       <c r="D37" s="26" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
       <c r="P37" s="19"/>
       <c r="S37" s="19"/>
     </row>
     <row r="38" spans="1:19">
       <c r="B38" s="3">
-        <v>10100004</v>
-      </c>
-      <c r="C38" s="19"/>
+        <v>10100003</v>
+      </c>
       <c r="D38" s="26" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="P38" s="27"/>
+        <v>58</v>
+      </c>
+      <c r="P38" s="19"/>
       <c r="S38" s="19"/>
     </row>
     <row r="39" spans="1:19">
       <c r="B39" s="3">
-        <v>10100005</v>
+        <v>10100004</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="26" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
@@ -2321,14 +2476,14 @@
     </row>
     <row r="40" spans="1:19">
       <c r="B40" s="3">
-        <v>10100006</v>
+        <v>10100005</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="26" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
@@ -2338,19 +2493,20 @@
       <c r="K40" s="19"/>
       <c r="L40" s="19"/>
       <c r="M40" s="19"/>
-      <c r="P40" s="19"/>
+      <c r="P40" s="27"/>
       <c r="S40" s="19"/>
     </row>
-    <row r="41" customFormat="1" spans="1:19">
-      <c r="A41" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>69</v>
+    <row r="41" spans="1:19">
+      <c r="B41" s="3">
+        <v>10100006</v>
       </c>
       <c r="C41" s="19"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="3"/>
+      <c r="D41" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="F41" s="19"/>
       <c r="G41" s="19"/>
       <c r="H41" s="19"/>
@@ -2362,17 +2518,16 @@
       <c r="P41" s="19"/>
       <c r="S41" s="19"/>
     </row>
-    <row r="42" s="3" customFormat="1" spans="1:19">
-      <c r="B42" s="3">
-        <v>11000001</v>
+    <row r="42" customFormat="1" spans="1:19">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C42" s="19"/>
-      <c r="D42" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="D42" s="26"/>
+      <c r="E42" s="3"/>
       <c r="F42" s="19"/>
       <c r="G42" s="19"/>
       <c r="H42" s="19"/>
@@ -2384,23 +2539,39 @@
       <c r="P42" s="19"/>
       <c r="S42" s="19"/>
     </row>
-    <row r="43" customFormat="1" spans="1:19">
+    <row r="43" s="3" customFormat="1" spans="1:19">
       <c r="B43" s="3">
+        <v>11000001</v>
+      </c>
+      <c r="C43" s="19"/>
+      <c r="D43" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="S43" s="19"/>
+    </row>
+    <row r="44" customFormat="1" spans="1:19">
+      <c r="B44" s="3">
         <v>11000002</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19">
-      <c r="B44"/>
-      <c r="C44"/>
-      <c r="D44" s="28"/>
-      <c r="E44"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="45" spans="1:19">
       <c r="B45"/>
@@ -2479,6 +2650,12 @@
       <c r="C57"/>
       <c r="D57" s="28"/>
       <c r="E57"/>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58" s="28"/>
+      <c r="E58"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2496,7 +2673,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO34"/>
+  <dimension ref="A1:AO35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2658,15 +2835,11 @@
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="7"/>
       <c r="E4" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -2709,31 +2882,33 @@
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8">
+        <v>3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="8">
+        <v>5</v>
+      </c>
+      <c r="K5" s="8">
+        <v>6</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
@@ -2766,230 +2941,295 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" spans="1:41">
-      <c r="B6" s="3">
-        <v>40000001</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>74</v>
-      </c>
+    <row r="6" s="1" customFormat="1" spans="1:41">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="8" t="str" cm="1">
+        <f t="array" ref="E6">INDEX([1]语言地区!$K:$K,MATCH(E5,[1]语言地区!$J:$J,0))</f>
+        <v>中国</v>
+      </c>
+      <c r="F6" s="8" t="str" cm="1">
+        <f t="array" ref="F6">INDEX([1]语言地区!$K:$K,MATCH(F5,[1]语言地区!$J:$J,0))</f>
+        <v>欧美</v>
+      </c>
+      <c r="G6" s="8" t="str" cm="1">
+        <f t="array" ref="G6">INDEX([1]语言地区!$K:$K,MATCH(G5,[1]语言地区!$J:$J,0))</f>
+        <v>港澳台</v>
+      </c>
+      <c r="H6" s="8" t="str" cm="1">
+        <f t="array" ref="H6">INDEX([1]语言地区!$K:$K,MATCH(H5,[1]语言地区!$J:$J,0))</f>
+        <v>韩国</v>
+      </c>
+      <c r="I6" s="8" t="str" cm="1">
+        <f t="array" ref="I6">INDEX([1]语言地区!$K:$K,MATCH(I5,[1]语言地区!$J:$J,0))</f>
+        <v>日本</v>
+      </c>
+      <c r="J6" s="8" t="str" cm="1">
+        <f t="array" ref="J6">INDEX([1]语言地区!$K:$K,MATCH(J5,[1]语言地区!$J:$J,0))</f>
+        <v>越南</v>
+      </c>
+      <c r="K6" s="8" t="str" cm="1">
+        <f t="array" ref="K6">INDEX([1]语言地区!$K:$K,MATCH(K5,[1]语言地区!$J:$J,0))</f>
+        <v>印尼</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
     </row>
     <row r="7" spans="1:41">
       <c r="B7" s="3">
-        <v>40000002</v>
+        <v>40000001</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:41">
       <c r="B8" s="3">
-        <v>40000003</v>
+        <v>40000002</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:41">
       <c r="B9" s="3">
-        <v>40000004</v>
+        <v>40000003</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:41">
       <c r="B10" s="3">
-        <v>40000005</v>
+        <v>40000004</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:41">
       <c r="B11" s="3">
-        <v>40000006</v>
+        <v>40000005</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:41">
       <c r="B12" s="3">
-        <v>40000007</v>
+        <v>40000006</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:41">
       <c r="B13" s="3">
-        <v>40000008</v>
+        <v>40000007</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:41">
       <c r="B14" s="3">
-        <v>40000009</v>
+        <v>40000008</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:41">
       <c r="B15" s="3">
-        <v>40000010</v>
+        <v>40000009</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:41">
       <c r="B16" s="3">
-        <v>40000011</v>
+        <v>40000010</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="3">
-        <v>40000012</v>
+        <v>40000011</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="B18" s="3">
-        <v>40000013</v>
+        <v>40000012</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="3">
-        <v>40000014</v>
+        <v>40000013</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:5">
-      <c r="A20" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" s="3">
+        <v>40000014</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="20"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:5">
-      <c r="B21" s="3">
+      <c r="B21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="20"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:5">
+      <c r="B22" s="3">
         <v>41000001</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="B22" s="3">
-        <v>41000002</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="B23" s="3">
-        <v>41000003</v>
+        <v>41000002</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="B24" s="3">
+        <v>41000003</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" s="3">
         <v>41000004</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
       <c r="B26" s="3"/>
@@ -3017,6 +3257,9 @@
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3033,7 +3276,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO47"/>
+  <dimension ref="A1:AO48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="16.6666666666667" customWidth="1"/>
@@ -3194,17 +3437,11 @@
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -3247,31 +3484,35 @@
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="D5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
+        <v>86</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8">
+        <v>3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="8">
+        <v>5</v>
+      </c>
+      <c r="K5" s="8">
+        <v>6</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
@@ -3304,8 +3545,73 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="31" spans="4:4">
-      <c r="D31" s="20"/>
+    <row r="6" s="1" customFormat="1" spans="1:41">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="8" t="str" cm="1">
+        <f t="array" ref="E6">INDEX([1]语言地区!$K:$K,MATCH(E5,[1]语言地区!$J:$J,0))</f>
+        <v>中国</v>
+      </c>
+      <c r="F6" s="8" t="str" cm="1">
+        <f t="array" ref="F6">INDEX([1]语言地区!$K:$K,MATCH(F5,[1]语言地区!$J:$J,0))</f>
+        <v>欧美</v>
+      </c>
+      <c r="G6" s="8" t="str" cm="1">
+        <f t="array" ref="G6">INDEX([1]语言地区!$K:$K,MATCH(G5,[1]语言地区!$J:$J,0))</f>
+        <v>港澳台</v>
+      </c>
+      <c r="H6" s="8" t="str" cm="1">
+        <f t="array" ref="H6">INDEX([1]语言地区!$K:$K,MATCH(H5,[1]语言地区!$J:$J,0))</f>
+        <v>韩国</v>
+      </c>
+      <c r="I6" s="8" t="str" cm="1">
+        <f t="array" ref="I6">INDEX([1]语言地区!$K:$K,MATCH(I5,[1]语言地区!$J:$J,0))</f>
+        <v>日本</v>
+      </c>
+      <c r="J6" s="8" t="str" cm="1">
+        <f t="array" ref="J6">INDEX([1]语言地区!$K:$K,MATCH(J5,[1]语言地区!$J:$J,0))</f>
+        <v>越南</v>
+      </c>
+      <c r="K6" s="8" t="str" cm="1">
+        <f t="array" ref="K6">INDEX([1]语言地区!$K:$K,MATCH(K5,[1]语言地区!$J:$J,0))</f>
+        <v>印尼</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" s="20"/>
@@ -3354,6 +3660,9 @@
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="20"/>
+    </row>
+    <row r="48" spans="4:4">
+      <c r="D48" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3370,7 +3679,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO47"/>
+  <dimension ref="A1:AO48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="38.5833333333333" style="4" customWidth="1"/>
@@ -3529,17 +3838,11 @@
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -3582,31 +3885,35 @@
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="D5" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
+        <v>86</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8">
+        <v>3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="8">
+        <v>5</v>
+      </c>
+      <c r="K5" s="8">
+        <v>6</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
@@ -3639,8 +3946,73 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="31" spans="4:4">
-      <c r="D31" s="20"/>
+    <row r="6" s="1" customFormat="1" spans="1:41">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="8" t="str" cm="1">
+        <f t="array" ref="E6">INDEX([1]语言地区!$K:$K,MATCH(E5,[1]语言地区!$J:$J,0))</f>
+        <v>中国</v>
+      </c>
+      <c r="F6" s="8" t="str" cm="1">
+        <f t="array" ref="F6">INDEX([1]语言地区!$K:$K,MATCH(F5,[1]语言地区!$J:$J,0))</f>
+        <v>欧美</v>
+      </c>
+      <c r="G6" s="8" t="str" cm="1">
+        <f t="array" ref="G6">INDEX([1]语言地区!$K:$K,MATCH(G5,[1]语言地区!$J:$J,0))</f>
+        <v>港澳台</v>
+      </c>
+      <c r="H6" s="8" t="str" cm="1">
+        <f t="array" ref="H6">INDEX([1]语言地区!$K:$K,MATCH(H5,[1]语言地区!$J:$J,0))</f>
+        <v>韩国</v>
+      </c>
+      <c r="I6" s="8" t="str" cm="1">
+        <f t="array" ref="I6">INDEX([1]语言地区!$K:$K,MATCH(I5,[1]语言地区!$J:$J,0))</f>
+        <v>日本</v>
+      </c>
+      <c r="J6" s="8" t="str" cm="1">
+        <f t="array" ref="J6">INDEX([1]语言地区!$K:$K,MATCH(J5,[1]语言地区!$J:$J,0))</f>
+        <v>越南</v>
+      </c>
+      <c r="K6" s="8" t="str" cm="1">
+        <f t="array" ref="K6">INDEX([1]语言地区!$K:$K,MATCH(K5,[1]语言地区!$J:$J,0))</f>
+        <v>印尼</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" s="20"/>
@@ -3689,6 +4061,9 @@
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="20"/>
+    </row>
+    <row r="48" spans="4:4">
+      <c r="D48" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3705,13 +4080,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO47"/>
+  <dimension ref="A1:AO48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="8.66666666666667" style="3"/>
     <col min="4" max="4" width="33" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20.8333333333333" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="8.66666666666667" style="3"/>
+    <col min="5" max="5" width="31.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.66666666666667" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:41">
@@ -3867,17 +4243,11 @@
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -3920,31 +4290,35 @@
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="D5" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
+        <v>86</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8">
+        <v>3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="8">
+        <v>5</v>
+      </c>
+      <c r="K5" s="8">
+        <v>6</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
@@ -3977,40 +4351,105 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" spans="1:41">
-      <c r="B6" s="3">
-        <v>1001</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>97</v>
-      </c>
+    <row r="6" s="1" customFormat="1" spans="1:41">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="8" t="str" cm="1">
+        <f t="array" ref="E6">INDEX([1]语言地区!$K:$K,MATCH(E5,[1]语言地区!$J:$J,0))</f>
+        <v>中国</v>
+      </c>
+      <c r="F6" s="8" t="str" cm="1">
+        <f t="array" ref="F6">INDEX([1]语言地区!$K:$K,MATCH(F5,[1]语言地区!$J:$J,0))</f>
+        <v>欧美</v>
+      </c>
+      <c r="G6" s="8" t="str" cm="1">
+        <f t="array" ref="G6">INDEX([1]语言地区!$K:$K,MATCH(G5,[1]语言地区!$J:$J,0))</f>
+        <v>港澳台</v>
+      </c>
+      <c r="H6" s="8" t="str" cm="1">
+        <f t="array" ref="H6">INDEX([1]语言地区!$K:$K,MATCH(H5,[1]语言地区!$J:$J,0))</f>
+        <v>韩国</v>
+      </c>
+      <c r="I6" s="8" t="str" cm="1">
+        <f t="array" ref="I6">INDEX([1]语言地区!$K:$K,MATCH(I5,[1]语言地区!$J:$J,0))</f>
+        <v>日本</v>
+      </c>
+      <c r="J6" s="8" t="str" cm="1">
+        <f t="array" ref="J6">INDEX([1]语言地区!$K:$K,MATCH(J5,[1]语言地区!$J:$J,0))</f>
+        <v>越南</v>
+      </c>
+      <c r="K6" s="8" t="str" cm="1">
+        <f t="array" ref="K6">INDEX([1]语言地区!$K:$K,MATCH(K5,[1]语言地区!$J:$J,0))</f>
+        <v>印尼</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
     </row>
     <row r="7" spans="1:41">
       <c r="B7" s="3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:41">
       <c r="B8" s="3">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:41">
       <c r="B9" s="3">
+        <v>1003</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41">
+      <c r="B10" s="3">
         <v>1004</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="4:4">
-      <c r="D31" s="20"/>
+      <c r="E10" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" s="20"/>
@@ -4059,6 +4498,9 @@
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="20"/>
+    </row>
+    <row r="48" spans="4:4">
+      <c r="D48" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/GameConfig/Datas/通用配置表/文本配置表.xlsx
+++ b/GameConfig/Datas/通用配置表/文本配置表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用配置表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2EAD63-DB0C-4677-A611-E28F31FED241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用文本" sheetId="1" r:id="rId1"/>
@@ -34,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="115">
   <si>
     <t>##var</t>
   </si>
@@ -328,29 +334,110 @@
     <t>服务器错误码文本，低位数自定义</t>
   </si>
   <si>
-    <t>账号参数不合法</t>
-  </si>
-  <si>
-    <t>用户名已存在</t>
-  </si>
-  <si>
-    <t>操作过于频繁</t>
-  </si>
-  <si>
-    <t>用户名或者密码错误</t>
+    <t>##</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号相关错误码</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号已存在</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>未知错误</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数无效，账号或密码为空</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>密码错误，请重试</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号不存在</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号已存在但密码错误</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置错误</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号已在线</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号或密码不能为空</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号格式不正确，需6-24位字母和数字</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>密码长度至少需8位</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>两次输入的密码不一致</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>注册成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色相关错误码</t>
+  </si>
+  <si>
+    <t>创建角色成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色配置不存在</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色名已存在</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色名无效（为空或包含非法字符）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>性别参数无效</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色不存在</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色不属于该账号</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色名长度不符，请使用中文2-6字，英文4-12字符</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色名字含有非法字符</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,6 +449,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -369,141 +457,27 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -524,186 +498,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -761,258 +573,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1021,46 +597,31 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="23" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1072,13 +633,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1091,69 +652,57 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="通用"/>
@@ -1512,33 +1061,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AO58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.5833333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.58203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="11" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.5833333333333" style="21" customWidth="1"/>
-    <col min="5" max="5" width="34.0833333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.58203125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="34.08203125" style="3" customWidth="1"/>
     <col min="6" max="11" width="35.25" style="3" customWidth="1"/>
     <col min="12" max="12" width="17.75" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.4166666666667" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.5833333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.4140625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.58203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="18.75" style="3" customWidth="1"/>
     <col min="16" max="16" width="16.5" style="3" customWidth="1"/>
-    <col min="17" max="17" width="13.1666666666667" style="3" customWidth="1"/>
-    <col min="18" max="18" width="17.9166666666667" style="3" customWidth="1"/>
+    <col min="17" max="17" width="13.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="17.9140625" style="3" customWidth="1"/>
     <col min="19" max="19" width="28" style="3" customWidth="1"/>
     <col min="20" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:41">
+    <row r="1" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1548,18 +1097,18 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -1568,7 +1117,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
-      <c r="T1" s="10"/>
+      <c r="T1" s="9"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
@@ -1591,35 +1140,35 @@
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:41">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="18"/>
+      <c r="E2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="10"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="9"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1642,29 +1191,29 @@
       <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:41">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="9"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1687,22 +1236,26 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:41">
+    <row r="4" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="8" t="s">
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1711,7 +1264,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="10"/>
+      <c r="T4" s="9"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1734,17 +1287,13 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:41">
+    <row r="5" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="22" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="8">
@@ -1776,7 +1325,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="10"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1799,13 +1348,13 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:41">
+    <row r="6" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="17" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="8" t="str" cm="1">
@@ -1844,7 +1393,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="10"/>
+      <c r="T6" s="9"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1867,7 +1416,7 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>10000001</v>
       </c>
@@ -1877,16 +1426,16 @@
       <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="S7" s="19"/>
-    </row>
-    <row r="8" spans="1:41">
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="S7" s="14"/>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>10000002</v>
       </c>
@@ -1896,16 +1445,16 @@
       <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="S8" s="19"/>
-    </row>
-    <row r="9" spans="1:41">
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="S8" s="14"/>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>10000003</v>
       </c>
@@ -1915,16 +1464,16 @@
       <c r="E9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="S9" s="19"/>
-    </row>
-    <row r="10" spans="1:41">
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="S9" s="14"/>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>10000004</v>
       </c>
@@ -1934,16 +1483,16 @@
       <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="S10" s="19"/>
-    </row>
-    <row r="11" spans="1:41">
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="S10" s="14"/>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>10000005</v>
       </c>
@@ -1953,16 +1502,16 @@
       <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="S11" s="19"/>
-    </row>
-    <row r="12" spans="1:41">
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="S11" s="14"/>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>10000006</v>
       </c>
@@ -1972,16 +1521,16 @@
       <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="S12" s="19"/>
-    </row>
-    <row r="13" spans="1:41">
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="S12" s="14"/>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <v>10000007</v>
       </c>
@@ -1991,208 +1540,208 @@
       <c r="E13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="S13" s="19"/>
-    </row>
-    <row r="14" spans="1:41">
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="S13" s="14"/>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>10000008</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="S14" s="19"/>
-    </row>
-    <row r="15" spans="1:41">
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="S14" s="14"/>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <v>10000009</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="S15" s="19"/>
-    </row>
-    <row r="16" spans="1:41">
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="S15" s="14"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>10000010</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="S16" s="19"/>
-    </row>
-    <row r="17" spans="2:19">
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="S16" s="14"/>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>10000011</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="S17" s="19"/>
-    </row>
-    <row r="18" spans="2:19">
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="S17" s="14"/>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>10000012</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="S18" s="19"/>
-    </row>
-    <row r="19" spans="2:19">
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="S18" s="14"/>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <v>10000013</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="S19" s="19"/>
-    </row>
-    <row r="20" spans="2:19">
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="S19" s="14"/>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <v>10000014</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="S20" s="19"/>
-    </row>
-    <row r="21" spans="2:19">
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="S20" s="14"/>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <v>10000015</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="S21" s="19"/>
-    </row>
-    <row r="22" spans="2:19">
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="S21" s="14"/>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <v>10000016</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="S22" s="19"/>
-    </row>
-    <row r="23" spans="2:19">
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="S22" s="14"/>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <v>10000017</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="S23" s="19"/>
-    </row>
-    <row r="24" spans="2:19">
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="S23" s="14"/>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <v>10000018</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="S24" s="19"/>
-    </row>
-    <row r="25" spans="2:19">
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="S24" s="14"/>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <v>10000019</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="S25" s="19"/>
-    </row>
-    <row r="26" spans="2:19">
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="P25" s="14"/>
+      <c r="S25" s="14"/>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <v>10000020</v>
       </c>
@@ -2202,16 +1751,16 @@
       <c r="E26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="S26" s="19"/>
-    </row>
-    <row r="27" spans="2:19">
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="S26" s="14"/>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <v>10000021</v>
       </c>
@@ -2221,16 +1770,16 @@
       <c r="E27" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="S27" s="19"/>
-    </row>
-    <row r="28" spans="2:19">
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="S27" s="14"/>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <v>10000022</v>
       </c>
@@ -2240,16 +1789,16 @@
       <c r="E28" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="S28" s="19"/>
-    </row>
-    <row r="29" spans="2:19">
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="S28" s="14"/>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
         <v>10000023</v>
       </c>
@@ -2259,16 +1808,16 @@
       <c r="E29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="S29" s="19"/>
-    </row>
-    <row r="30" spans="2:19">
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="S29" s="14"/>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <v>10000024</v>
       </c>
@@ -2278,16 +1827,16 @@
       <c r="E30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="S30" s="19"/>
-    </row>
-    <row r="31" spans="2:19">
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="S30" s="14"/>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31" s="3">
         <v>10000025</v>
       </c>
@@ -2297,16 +1846,16 @@
       <c r="E31" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="S31" s="19"/>
-    </row>
-    <row r="32" spans="2:19">
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="S31" s="14"/>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" s="3">
         <v>10000026</v>
       </c>
@@ -2316,345 +1865,345 @@
       <c r="E32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="S32" s="19"/>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="S32" s="14"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B33" s="3">
         <v>10000027</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="E33" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F33" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="G33" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="H33" s="19" t="s">
+      <c r="H33" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="19" t="s">
+      <c r="I33" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="19" t="s">
+      <c r="J33" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K33" s="19" t="s">
+      <c r="K33" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="P33" s="19"/>
-      <c r="S33" s="19"/>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="P33" s="14"/>
+      <c r="S33" s="14"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B34" s="3">
         <v>10000028</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E34" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I34" s="19" t="s">
+      <c r="I34" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J34" s="19" t="s">
+      <c r="J34" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K34" s="19" t="s">
+      <c r="K34" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="P34" s="19"/>
-      <c r="S34" s="19"/>
-    </row>
-    <row r="35" customFormat="1" spans="1:19">
+      <c r="P34" s="14"/>
+      <c r="S34" s="14"/>
+    </row>
+    <row r="35" spans="1:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
       <c r="B35" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="S35" s="19"/>
-    </row>
-    <row r="36" s="3" customFormat="1" spans="1:19">
+      <c r="D35" s="16"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="S35" s="14"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B36" s="3">
         <v>10100001</v>
       </c>
-      <c r="D36" s="26" t="s">
+      <c r="D36" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="25" t="s">
+      <c r="E36" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="S36" s="19"/>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="S36" s="14"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B37" s="3">
         <v>10100002</v>
       </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="26" t="s">
+      <c r="C37" s="14"/>
+      <c r="D37" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="S37" s="19"/>
-    </row>
-    <row r="38" spans="1:19">
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="S37" s="14"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B38" s="3">
         <v>10100003</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="D38" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="P38" s="19"/>
-      <c r="S38" s="19"/>
-    </row>
-    <row r="39" spans="1:19">
+      <c r="P38" s="14"/>
+      <c r="S38" s="14"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B39" s="3">
         <v>10100004</v>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="26" t="s">
+      <c r="C39" s="14"/>
+      <c r="D39" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="P39" s="27"/>
-      <c r="S39" s="19"/>
-    </row>
-    <row r="40" spans="1:19">
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="P39" s="22"/>
+      <c r="S39" s="14"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B40" s="3">
         <v>10100005</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="26" t="s">
+      <c r="C40" s="14"/>
+      <c r="D40" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="P40" s="27"/>
-      <c r="S40" s="19"/>
-    </row>
-    <row r="41" spans="1:19">
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="P40" s="22"/>
+      <c r="S40" s="14"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B41" s="3">
         <v>10100006</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="26" t="s">
+      <c r="C41" s="14"/>
+      <c r="D41" s="21" t="s">
         <v>55</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="S41" s="19"/>
-    </row>
-    <row r="42" customFormat="1" spans="1:19">
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="P41" s="14"/>
+      <c r="S41" s="14"/>
+    </row>
+    <row r="42" spans="1:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>9</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="26"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="S42" s="19"/>
-    </row>
-    <row r="43" s="3" customFormat="1" spans="1:19">
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="P42" s="14"/>
+      <c r="S42" s="14"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B43" s="3">
         <v>11000001</v>
       </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="26" t="s">
+      <c r="C43" s="14"/>
+      <c r="D43" s="21" t="s">
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="P43" s="19"/>
-      <c r="S43" s="19"/>
-    </row>
-    <row r="44" customFormat="1" spans="1:19">
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="P43" s="14"/>
+      <c r="S43" s="14"/>
+    </row>
+    <row r="44" spans="1:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3">
         <v>11000002</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="26" t="s">
+      <c r="D44" s="21" t="s">
         <v>62</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B45"/>
       <c r="C45"/>
-      <c r="D45" s="28"/>
+      <c r="D45" s="23"/>
       <c r="E45"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B46"/>
       <c r="C46"/>
-      <c r="D46" s="28"/>
+      <c r="D46" s="23"/>
       <c r="E46"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B47"/>
       <c r="C47"/>
-      <c r="D47" s="28"/>
+      <c r="D47" s="23"/>
       <c r="E47"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B48"/>
       <c r="C48"/>
-      <c r="D48" s="28"/>
+      <c r="D48" s="23"/>
       <c r="E48"/>
     </row>
-    <row r="49" spans="2:5">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49"/>
       <c r="C49"/>
-      <c r="D49" s="28"/>
+      <c r="D49" s="23"/>
       <c r="E49"/>
     </row>
-    <row r="50" spans="2:5">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50"/>
       <c r="C50"/>
-      <c r="D50" s="28"/>
+      <c r="D50" s="23"/>
       <c r="E50"/>
     </row>
-    <row r="51" spans="2:5">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51"/>
       <c r="C51"/>
-      <c r="D51" s="28"/>
+      <c r="D51" s="23"/>
       <c r="E51"/>
     </row>
-    <row r="52" spans="2:5">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52"/>
       <c r="C52"/>
-      <c r="D52" s="28"/>
+      <c r="D52" s="23"/>
       <c r="E52"/>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53"/>
       <c r="C53"/>
-      <c r="D53" s="28"/>
+      <c r="D53" s="23"/>
       <c r="E53"/>
     </row>
-    <row r="54" spans="2:5">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54"/>
       <c r="C54"/>
-      <c r="D54" s="28"/>
+      <c r="D54" s="23"/>
       <c r="E54"/>
     </row>
-    <row r="55" spans="2:5">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55"/>
       <c r="C55"/>
-      <c r="D55" s="28"/>
+      <c r="D55" s="23"/>
       <c r="E55"/>
     </row>
-    <row r="56" spans="2:5">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56"/>
       <c r="C56"/>
-      <c r="D56" s="28"/>
+      <c r="D56" s="23"/>
       <c r="E56"/>
     </row>
-    <row r="57" spans="2:5">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57"/>
       <c r="C57"/>
-      <c r="D57" s="28"/>
+      <c r="D57" s="23"/>
       <c r="E57"/>
     </row>
-    <row r="58" spans="2:5">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58"/>
       <c r="C58"/>
-      <c r="D58" s="28"/>
+      <c r="D58" s="23"/>
       <c r="E58"/>
     </row>
   </sheetData>
@@ -2664,25 +2213,24 @@
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="E4:K4"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AO35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
     <col min="4" max="4" width="41.75" customWidth="1"/>
-    <col min="5" max="5" width="51.875" customWidth="1"/>
+    <col min="5" max="5" width="51.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:41">
+    <row r="1" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2695,15 +2243,15 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -2712,7 +2260,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
-      <c r="T1" s="10"/>
+      <c r="T1" s="9"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
@@ -2735,35 +2283,35 @@
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:41">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="10"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="9"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -2786,29 +2334,29 @@
       <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:41">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="9"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -2831,22 +2379,26 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:41">
+    <row r="4" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -2855,7 +2407,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="10"/>
+      <c r="T4" s="9"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -2878,16 +2430,12 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:41">
+    <row r="5" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="7"/>
       <c r="E5" s="8">
         <v>0</v>
@@ -2918,7 +2466,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="10"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -2941,7 +2489,7 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:41">
+    <row r="6" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -2986,7 +2534,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="10"/>
+      <c r="T6" s="9"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -3009,185 +2557,184 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>40000001</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>40000002</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>40000003</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>40000004</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:41">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>40000005</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:41">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>40000006</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:41">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <v>40000007</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:41">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>40000008</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:41">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <v>40000009</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:41">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>40000010</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>40000011</v>
       </c>
       <c r="C17" s="3"/>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>40000012</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <v>40000013</v>
       </c>
       <c r="C19" s="3"/>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <v>40000014</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" s="3" customFormat="1" spans="1:5">
+    <row r="21" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="20"/>
-    </row>
-    <row r="22" customFormat="1" spans="1:5">
+      <c r="D21" s="15"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <v>41000001</v>
       </c>
@@ -3198,7 +2745,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <v>41000002</v>
       </c>
@@ -3209,7 +2756,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <v>41000003</v>
       </c>
@@ -3220,7 +2767,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <v>41000004</v>
       </c>
@@ -3231,34 +2778,34 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
     </row>
   </sheetData>
@@ -3268,23 +2815,22 @@
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="E4:K4"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AO48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="32.5833333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="32.58203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:41">
+    <row r="1" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3297,15 +2843,15 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -3314,7 +2860,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
-      <c r="T1" s="10"/>
+      <c r="T1" s="9"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
@@ -3337,35 +2883,35 @@
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:41">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="10"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="9"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -3388,29 +2934,29 @@
       <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:41">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="9"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -3433,22 +2979,26 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:41">
+    <row r="4" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -3457,7 +3007,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="10"/>
+      <c r="T4" s="9"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -3480,16 +3030,12 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:41">
+    <row r="5" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="7" t="s">
         <v>86</v>
       </c>
@@ -3522,7 +3068,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="10"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -3545,7 +3091,7 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:41">
+    <row r="6" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -3590,7 +3136,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="10"/>
+      <c r="T6" s="9"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -3613,56 +3159,56 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
     </row>
-    <row r="32" spans="4:4">
-      <c r="D32" s="20"/>
-    </row>
-    <row r="33" spans="4:4">
-      <c r="D33" s="20"/>
-    </row>
-    <row r="34" spans="4:4">
-      <c r="D34" s="20"/>
-    </row>
-    <row r="35" spans="4:4">
-      <c r="D35" s="20"/>
-    </row>
-    <row r="36" spans="4:4">
-      <c r="D36" s="20"/>
-    </row>
-    <row r="37" spans="4:4">
-      <c r="D37" s="20"/>
-    </row>
-    <row r="38" spans="4:4">
-      <c r="D38" s="20"/>
-    </row>
-    <row r="39" spans="4:4">
-      <c r="D39" s="20"/>
-    </row>
-    <row r="40" spans="4:4">
-      <c r="D40" s="20"/>
-    </row>
-    <row r="41" spans="4:4">
-      <c r="D41" s="20"/>
-    </row>
-    <row r="42" spans="4:4">
-      <c r="D42" s="20"/>
-    </row>
-    <row r="43" spans="4:4">
-      <c r="D43" s="20"/>
-    </row>
-    <row r="44" spans="4:4">
-      <c r="D44" s="20"/>
-    </row>
-    <row r="45" spans="4:4">
-      <c r="D45" s="20"/>
-    </row>
-    <row r="46" spans="4:4">
-      <c r="D46" s="20"/>
-    </row>
-    <row r="47" spans="4:4">
-      <c r="D47" s="20"/>
-    </row>
-    <row r="48" spans="4:4">
-      <c r="D48" s="20"/>
+    <row r="32" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D32" s="15"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="15"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="15"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="15"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="15"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D37" s="15"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="15"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="15"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="15"/>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D41" s="15"/>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D42" s="15"/>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D43" s="15"/>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D45" s="15"/>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D46" s="15"/>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D47" s="15"/>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D48" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3671,21 +3217,20 @@
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="E4:K4"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AO48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="38.5833333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="38.58203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:41">
+    <row r="1" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3698,15 +3243,15 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -3715,7 +3260,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
-      <c r="T1" s="10"/>
+      <c r="T1" s="9"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
@@ -3738,35 +3283,35 @@
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:41">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="10"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="9"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -3789,29 +3334,29 @@
       <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:41">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="9"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -3834,22 +3379,26 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:41">
+    <row r="4" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -3858,7 +3407,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="10"/>
+      <c r="T4" s="9"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -3881,16 +3430,12 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:41">
+    <row r="5" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="7" t="s">
         <v>86</v>
       </c>
@@ -3923,7 +3468,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="10"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -3946,7 +3491,7 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:41">
+    <row r="6" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -3991,7 +3536,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="10"/>
+      <c r="T6" s="9"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -4014,56 +3559,56 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
     </row>
-    <row r="32" spans="4:4">
-      <c r="D32" s="20"/>
-    </row>
-    <row r="33" spans="4:4">
-      <c r="D33" s="20"/>
-    </row>
-    <row r="34" spans="4:4">
-      <c r="D34" s="20"/>
-    </row>
-    <row r="35" spans="4:4">
-      <c r="D35" s="20"/>
-    </row>
-    <row r="36" spans="4:4">
-      <c r="D36" s="20"/>
-    </row>
-    <row r="37" spans="4:4">
-      <c r="D37" s="20"/>
-    </row>
-    <row r="38" spans="4:4">
-      <c r="D38" s="20"/>
-    </row>
-    <row r="39" spans="4:4">
-      <c r="D39" s="20"/>
-    </row>
-    <row r="40" spans="4:4">
-      <c r="D40" s="20"/>
-    </row>
-    <row r="41" spans="4:4">
-      <c r="D41" s="20"/>
-    </row>
-    <row r="42" spans="4:4">
-      <c r="D42" s="20"/>
-    </row>
-    <row r="43" spans="4:4">
-      <c r="D43" s="20"/>
-    </row>
-    <row r="44" spans="4:4">
-      <c r="D44" s="20"/>
-    </row>
-    <row r="45" spans="4:4">
-      <c r="D45" s="20"/>
-    </row>
-    <row r="46" spans="4:4">
-      <c r="D46" s="20"/>
-    </row>
-    <row r="47" spans="4:4">
-      <c r="D47" s="20"/>
-    </row>
-    <row r="48" spans="4:4">
-      <c r="D48" s="20"/>
+    <row r="32" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D32" s="15"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="15"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="15"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="15"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="15"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D37" s="15"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="15"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="15"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="15"/>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D41" s="15"/>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D42" s="15"/>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D43" s="15"/>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D45" s="15"/>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D46" s="15"/>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D47" s="15"/>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D48" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4072,25 +3617,24 @@
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="E4:K4"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AO48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:AO49"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.66666666666667" style="3"/>
+    <col min="1" max="3" width="8.6640625" style="3"/>
     <col min="4" max="4" width="33" style="4" customWidth="1"/>
-    <col min="5" max="5" width="31.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.66666666666667" style="3"/>
+    <col min="5" max="5" width="39.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:41">
+    <row r="1" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4103,15 +3647,15 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -4120,7 +3664,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
-      <c r="T1" s="10"/>
+      <c r="T1" s="9"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
@@ -4143,35 +3687,35 @@
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:41">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="10"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="9"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -4194,29 +3738,29 @@
       <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:41">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="9"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -4239,22 +3783,26 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:41">
+    <row r="4" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -4263,7 +3811,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="10"/>
+      <c r="T4" s="9"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -4286,16 +3834,12 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:41">
+    <row r="5" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="7" t="s">
         <v>86</v>
       </c>
@@ -4328,7 +3872,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="10"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -4351,7 +3895,7 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:41">
+    <row r="6" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -4396,7 +3940,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="10"/>
+      <c r="T6" s="9"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -4419,88 +3963,332 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
     </row>
-    <row r="7" spans="1:41">
-      <c r="B7" s="3">
+    <row r="7" spans="1:41" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="25"/>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
         <v>1001</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="D8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <v>1002</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <v>1003</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <v>1004</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
+        <v>1005</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B13" s="3">
+        <v>1006</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
+        <v>1007</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
+        <v>1008</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
+        <v>1009</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <v>1010</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="3">
+        <v>1011</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
+        <v>1012</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
+        <v>1013</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>1014</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="27" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="1:41">
-      <c r="B8" s="3">
-        <v>1002</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:41">
-      <c r="B9" s="3">
-        <v>1003</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:41">
-      <c r="B10" s="3">
-        <v>1004</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="4:4">
-      <c r="D32" s="20"/>
-    </row>
-    <row r="33" spans="4:4">
-      <c r="D33" s="20"/>
-    </row>
-    <row r="34" spans="4:4">
-      <c r="D34" s="20"/>
-    </row>
-    <row r="35" spans="4:4">
-      <c r="D35" s="20"/>
-    </row>
-    <row r="36" spans="4:4">
-      <c r="D36" s="20"/>
-    </row>
-    <row r="37" spans="4:4">
-      <c r="D37" s="20"/>
-    </row>
-    <row r="38" spans="4:4">
-      <c r="D38" s="20"/>
-    </row>
-    <row r="39" spans="4:4">
-      <c r="D39" s="20"/>
-    </row>
-    <row r="40" spans="4:4">
-      <c r="D40" s="20"/>
-    </row>
-    <row r="41" spans="4:4">
-      <c r="D41" s="20"/>
-    </row>
-    <row r="42" spans="4:4">
-      <c r="D42" s="20"/>
-    </row>
-    <row r="43" spans="4:4">
-      <c r="D43" s="20"/>
-    </row>
-    <row r="44" spans="4:4">
-      <c r="D44" s="20"/>
-    </row>
-    <row r="45" spans="4:4">
-      <c r="D45" s="20"/>
-    </row>
-    <row r="46" spans="4:4">
-      <c r="D46" s="20"/>
-    </row>
-    <row r="47" spans="4:4">
-      <c r="D47" s="20"/>
-    </row>
-    <row r="48" spans="4:4">
-      <c r="D48" s="20"/>
+      <c r="E22" s="27"/>
+    </row>
+    <row r="23" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
+        <v>2001</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
+        <v>2002</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="3">
+        <v>2003</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>2004</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="3">
+        <v>2005</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
+        <v>2006</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="3">
+        <v>2007</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="3">
+        <v>2008</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="3">
+        <v>2009</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="15"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="15"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="15"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="15"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D37" s="15"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="15"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="15"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="15"/>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D41" s="15"/>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D42" s="15"/>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D43" s="15"/>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D45" s="15"/>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D46" s="15"/>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D47" s="15"/>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D48" s="15"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D49" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4509,7 +4297,7 @@
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="E4:K4"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>